--- a/7rmartSupermarket/src/test/resources/7RMartsupermarket.xlsx
+++ b/7rmartSupermarket/src/test/resources/7RMartsupermarket.xlsx
@@ -5,16 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anany\eclipse-workspace\7rmartSupermarket\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anany\git\Automation_7rMartApplication\7rmartSupermarket\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{701345A8-06C3-45F3-ACD8-F0B96A290C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27124FD5-2EAD-4802-83D9-E85922B69615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00371627-C0F8-442D-906F-2A2CE2AA46EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00371627-C0F8-442D-906F-2A2CE2AA46EA}"/>
   </bookViews>
   <sheets>
     <sheet name="loginpage" sheetId="1" r:id="rId1"/>
-    <sheet name="adminuserpage" sheetId="2" r:id="rId2"/>
+    <sheet name="managefootertextupdate" sheetId="3" r:id="rId2"/>
+    <sheet name="adminuserpage" sheetId="2" r:id="rId3"/>
+    <sheet name="managenewsaddnewspage" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
   <si>
     <t>Username</t>
   </si>
@@ -95,13 +97,52 @@
   </si>
   <si>
     <t>anu99</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>phonenumber</t>
+  </si>
+  <si>
+    <t>123 Test St</t>
+  </si>
+  <si>
+    <t>test@mail.com</t>
+  </si>
+  <si>
+    <t>FNmbr: 1207B, Confident</t>
+  </si>
+  <si>
+    <t>johnhonai@xy.com</t>
+  </si>
+  <si>
+    <t>romanth first block</t>
+  </si>
+  <si>
+    <t>romanathan@gmail.com</t>
+  </si>
+  <si>
+    <t>News</t>
+  </si>
+  <si>
+    <t>New Item added to the product list</t>
+  </si>
+  <si>
+    <t>Product name changed</t>
+  </si>
+  <si>
+    <t>Company logo updated</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,6 +154,26 @@
       <sz val="10"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2A00FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -132,14 +193,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -505,6 +573,68 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F172F6AA-CAF1-4A51-A587-62A77FFF8120}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.77734375" customWidth="1"/>
+    <col min="2" max="2" width="23.88671875" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2">
+        <v>9010803010</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3">
+        <v>956273687</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="2">
+        <v>6543267966</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B4" r:id="rId1" xr:uid="{70D375D6-6030-4DD5-AF00-02FF7DE0197A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49B7761-F1BA-4227-9DD3-55FD5CD15AD9}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -584,4 +714,37 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE2AFF09-0E52-4076-AA6A-8FF6DB5EB258}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/7rmartSupermarket/src/test/resources/7RMartsupermarket.xlsx
+++ b/7rmartSupermarket/src/test/resources/7RMartsupermarket.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anany\git\Automation_7rMartApplication\7rmartSupermarket\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27124FD5-2EAD-4802-83D9-E85922B69615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40D6E18-FACA-475D-9783-F25056D4FCAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00371627-C0F8-442D-906F-2A2CE2AA46EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{00371627-C0F8-442D-906F-2A2CE2AA46EA}"/>
   </bookViews>
   <sheets>
     <sheet name="loginpage" sheetId="1" r:id="rId1"/>
     <sheet name="managefootertextupdate" sheetId="3" r:id="rId2"/>
     <sheet name="adminuserpage" sheetId="2" r:id="rId3"/>
     <sheet name="managenewsaddnewspage" sheetId="4" r:id="rId4"/>
+    <sheet name="managecontactpage" sheetId="5" r:id="rId5"/>
+    <sheet name="managecategorypage" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="47">
   <si>
     <t>Username</t>
   </si>
@@ -136,6 +138,48 @@
   </si>
   <si>
     <t>Company logo updated</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>Delivery time</t>
+  </si>
+  <si>
+    <t>Delivery charge limit</t>
+  </si>
+  <si>
+    <t>kyler.botsford@hotmail.com</t>
+  </si>
+  <si>
+    <t>7684 Rolando Fork, New Erna, SD 46235</t>
+  </si>
+  <si>
+    <t>bobyxyz@gmail.com</t>
+  </si>
+  <si>
+    <t>1st block near st road</t>
+  </si>
+  <si>
+    <t>zayantara@gmail.com</t>
+  </si>
+  <si>
+    <t>1st block near kc road nyk</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>Berries</t>
+  </si>
+  <si>
+    <t>Citrus fruit</t>
+  </si>
+  <si>
+    <t>RiceCrop Category</t>
+  </si>
+  <si>
+    <t>Fruit Category</t>
   </si>
 </sst>
 </file>
@@ -197,13 +241,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -747,4 +794,133 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B54549E-610A-4805-843F-F29B44F12796}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.77734375" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="33.33203125" customWidth="1"/>
+    <col min="4" max="4" width="26.88671875" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>9889766754</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>6673674576</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>7233456755</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4">
+        <v>7</v>
+      </c>
+      <c r="E4">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{BEE51D3F-0B3B-41C9-8585-4C9887E4C8DC}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{D2376CBA-39D1-486A-8936-8117268045ED}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{6FC77D71-AC1B-4744-ADE4-A3B4FE3658E5}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC0F31AD-D26D-4BC1-B255-6BDACE162A98}">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.109375" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/7rmartSupermarket/src/test/resources/7RMartsupermarket.xlsx
+++ b/7rmartSupermarket/src/test/resources/7RMartsupermarket.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anany\git\Automation_7rMartApplication\7rmartSupermarket\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40D6E18-FACA-475D-9783-F25056D4FCAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C57E2C28-E427-4900-A26E-750D8FD31A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{00371627-C0F8-442D-906F-2A2CE2AA46EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00371627-C0F8-442D-906F-2A2CE2AA46EA}"/>
   </bookViews>
   <sheets>
     <sheet name="loginpage" sheetId="1" r:id="rId1"/>
@@ -71,9 +71,6 @@
     <t>ramya22</t>
   </si>
   <si>
-    <t>sanvi14</t>
-  </si>
-  <si>
     <t>sanvi20</t>
   </si>
   <si>
@@ -180,6 +177,9 @@
   </si>
   <si>
     <t>Fruit Category</t>
+  </si>
+  <si>
+    <t>sanvi143</t>
   </si>
 </sst>
 </file>
@@ -631,21 +631,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>21</v>
-      </c>
-      <c r="C1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
         <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
       </c>
       <c r="C2">
         <v>9010803010</v>
@@ -653,10 +653,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
         <v>25</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
       </c>
       <c r="C3">
         <v>956273687</v>
@@ -664,10 +664,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="C4" s="2">
         <v>6543267966</v>
@@ -715,10 +715,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
@@ -726,32 +726,32 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
         <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
       </c>
       <c r="C6" t="s">
         <v>2</v>
@@ -773,22 +773,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -810,19 +810,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>34</v>
-      </c>
-      <c r="E1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -830,10 +830,10 @@
         <v>9889766754</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
         <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>37</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -847,10 +847,10 @@
         <v>6673674576</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
         <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
       </c>
       <c r="D3">
         <v>4</v>
@@ -864,10 +864,10 @@
         <v>7233456755</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
         <v>40</v>
-      </c>
-      <c r="C4" t="s">
-        <v>41</v>
       </c>
       <c r="D4">
         <v>7</v>
@@ -897,27 +897,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
